--- a/tasks/finalpool/fetch-sf-kpi-dashboard-excel-word-email/groundtruth_workspace/KPI_Dashboard_Report.xlsx
+++ b/tasks/finalpool/fetch-sf-kpi-dashboard-excel-word-email/groundtruth_workspace/KPI_Dashboard_Report.xlsx
@@ -449,17 +449,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Total_Revenue</t>
+          <t>Employee_Satisfaction</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2500000</v>
+        <v>3.8</v>
       </c>
       <c r="C2" t="n">
-        <v>2200000</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>88</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -470,38 +470,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Avg_Order_Value</t>
+          <t>Support_Response_Time</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>85</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>83.18000000000001</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>97.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Near</t>
+          <t>Missed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Support_Response_Time</t>
+          <t>Total_Revenue</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>2500000</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>2200000</v>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -533,38 +533,38 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Employee_Satisfaction</t>
+          <t>Ticket_Resolution_Rate</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8</v>
+        <v>90</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="D6" t="n">
-        <v>78.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Missed</t>
+          <t>Near</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ticket_Resolution_Rate</t>
+          <t>Avg_Order_Value</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>82</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>91.09999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
